--- a/business_surveys/017_crop_storage_management_survey--business_surveys.xlsx
+++ b/business_surveys/017_crop_storage_management_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Storage Practices</t>
+          <t>Current Storage Method</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,58 +635,58 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>storage_capacity_1</t>
+          <t>storage_challenges_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Storage Capacity</t>
+          <t>Storage Challenges 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>storage_challenges_1</t>
+          <t>storage_facility_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Storage Challenges</t>
+          <t>Storage Facility 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>storage_facility_1</t>
+          <t>other_challenges</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Storage Facility</t>
+          <t>Other Challenges</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -707,12 +707,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -735,153 +735,204 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>storage_facility_choices</t>
+          <t>storage_practices_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'facility_1',_'value':_'facility_1'}</t>
+          <t>storage_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Facility 1', 'value': 'Facility 1'}</t>
+          <t>Storage 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>storage_facility_choices</t>
+          <t>storage_practices_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'facility_2',_'value':_'facility_2'}</t>
+          <t>storage_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Facility 2', 'value': 'Facility 2'}</t>
+          <t>Storage 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>storage_facility_choices</t>
+          <t>storage_practices_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'facility_3',_'value':_'facility_3'}</t>
+          <t>storage_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Facility 3', 'value': 'Facility 3'}</t>
+          <t>Storage 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>storage_practices_1_choices</t>
+          <t>storage_facility_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'practice_1',_'value':_'practice_1'}</t>
+          <t>facility_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Practice 1', 'value': 'Practice 1'}</t>
+          <t>Facility 1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>storage_practices_1_choices</t>
+          <t>storage_facility_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'practice_2',_'value':_'practice_2'}</t>
+          <t>facility_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Practice 2', 'value': 'Practice 2'}</t>
+          <t>Facility 2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>storage_practices_1_choices</t>
+          <t>storage_facility_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'practice_3',_'value':_'practice_3'}</t>
+          <t>facility_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Practice 3', 'value': 'Practice 3'}</t>
+          <t>Facility 3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>storage_facility_1_choices</t>
+          <t>storage_practices_1_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'facility_1',_'value':_'facility_1'}</t>
+          <t>practice_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Facility 1', 'value': 'Facility 1'}</t>
+          <t>Practice 1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>storage_facility_1_choices</t>
+          <t>storage_practices_1_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'facility_2',_'value':_'facility_2'}</t>
+          <t>practice_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Facility 2', 'value': 'Facility 2'}</t>
+          <t>Practice 2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>storage_practices_1_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>practice_3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Practice 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>storage_facility_1_choices</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'facility_3',_'value':_'facility_3'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'Facility 3', 'value': 'Facility 3'}</t>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>facility_1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Facility 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>storage_facility_1_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>facility_2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Facility 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>storage_facility_1_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>facility_3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Facility 3</t>
         </is>
       </c>
     </row>
